--- a/stories/arbres/TREE-FAM-007.xlsx
+++ b/stories/arbres/TREE-FAM-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est dans la cuisine. Un bocal est trop haut. C'est trop difficile. Léa va aller vers maman. Elle va dire le besoin : j'ai besoin d'aide. Maman écoute. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tabouret, l'évier, ou le placard.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le tabouret. Ça sent le pain. maman est tout près. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Léa ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Léa a retenu. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le bocal. Il y a des miettes. maman montre lentement. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2579,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2746,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. La lumière est claire. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2913,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3080,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Un oiseau chante. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3247,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3414,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Le sol est frais. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3581,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3748,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la boîte. Le bocal brille. maman montre lentement. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3939,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4106,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Un oiseau chante. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4273,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4440,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Le sol est frais. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4607,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4774,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Maman sourit. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4941,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5108,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le torchon. Le torchon est doux. maman montre lentement. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5299,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5466,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Le sol est frais. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5633,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5800,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Maman sourit. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5967,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6134,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Le lait est blanc. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6301,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6468,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers l'évier. L'eau coule. maman est tout près. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6479,6 +6651,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Léa ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6503,7 +6680,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Léa respire. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit : je suis là.</t>
+          <t>Léa respire. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6645,6 +6822,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Léa respire. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman.
+maman|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7014,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7181,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le bocal. La lumière est claire. maman montre lentement. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7372,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7539,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Un oiseau chante. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7706,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7873,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Le sol est frais. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8040,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8207,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Maman sourit. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8374,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8541,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la boîte. Un oiseau chante. maman montre lentement. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8732,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8899,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Le sol est frais. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9066,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9233,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Maman sourit. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9400,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9567,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Le lait est blanc. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9734,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9901,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le torchon. Le sol est frais. maman montre lentement. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10092,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10259,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Maman sourit. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10426,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10593,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Le lait est blanc. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10760,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10927,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Une cuillère tinte. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11094,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11261,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le placard. Le bois est lisse. maman est tout près. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11442,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Léa ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11615,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. Léa donne la main à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11806,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11973,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le bocal. Maman sourit. maman montre lentement. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12164,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12331,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Le sol est frais. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12498,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12665,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Maman sourit. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12832,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +12999,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Le lait est blanc. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13166,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13333,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la boîte. Le lait est blanc. maman montre lentement. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13524,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13691,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Maman sourit. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Le lait est blanc. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14192,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14359,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Une cuillère tinte. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14526,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14693,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le torchon. Une cuillère tinte. maman montre lentement. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14884,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15051,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un câlin. Le lait est blanc. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15218,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15385,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une aide. Une cuillère tinte. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15552,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15719,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint un mot. Ça sent le pain. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15886,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15926,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-007.xlsx
+++ b/stories/arbres/TREE-FAM-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Léa est dans la cuisine. Un bocal est trop haut. C'est trop difficile. Léa va aller vers maman. Elle va dire le besoin : j'ai besoin d'aide. Maman écoute. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le tabouret, l'évier, ou le placard.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Léa va vers le tabouret. Ça sent le pain. maman est tout près. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|C'est trop difficile. Que fait Léa ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Léa a retenu. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Léa a choisi le bocal. Il y a des miettes. maman montre lentement. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2584,6 +2596,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2751,6 +2764,7 @@
           <t>narrateur|Léa rejoint un câlin. La lumière est claire. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2918,6 +2932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3085,6 +3100,7 @@
           <t>narrateur|Léa rejoint une aide. Un oiseau chante. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3252,6 +3268,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3419,6 +3436,7 @@
           <t>narrateur|Léa rejoint un mot. Le sol est frais. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3586,6 +3604,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3753,6 +3772,7 @@
           <t>narrateur|Léa a choisi la boîte. Le bocal brille. maman montre lentement. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3944,6 +3964,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4111,6 +4132,7 @@
           <t>narrateur|Léa rejoint un câlin. Un oiseau chante. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4278,6 +4300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4445,6 +4468,7 @@
           <t>narrateur|Léa rejoint une aide. Le sol est frais. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4612,6 +4636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4779,6 +4804,7 @@
           <t>narrateur|Léa rejoint un mot. Maman sourit. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4946,6 +4972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5113,6 +5140,7 @@
           <t>narrateur|Léa a choisi le torchon. Le torchon est doux. maman montre lentement. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5304,6 +5332,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5471,6 +5500,7 @@
           <t>narrateur|Léa rejoint un câlin. Le sol est frais. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5638,6 +5668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5805,6 +5836,7 @@
           <t>narrateur|Léa rejoint une aide. Maman sourit. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5972,6 +6004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6139,6 +6172,7 @@
           <t>narrateur|Léa rejoint un mot. Le lait est blanc. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le tabouret, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6306,6 +6340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6473,6 +6508,7 @@
           <t>narrateur|Léa va vers l'évier. L'eau coule. maman est tout près. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6656,6 +6692,7 @@
           <t>narrateur|C'est trop difficile. Que fait Léa ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6828,6 +6865,7 @@
 maman|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7019,6 +7057,7 @@
           <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7186,6 +7225,7 @@
           <t>narrateur|Léa a choisi le bocal. La lumière est claire. maman montre lentement. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7377,6 +7417,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7544,6 +7585,7 @@
           <t>narrateur|Léa rejoint un câlin. Un oiseau chante. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7711,6 +7753,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7878,6 +7921,7 @@
           <t>narrateur|Léa rejoint une aide. Le sol est frais. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8045,6 +8089,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8212,6 +8257,7 @@
           <t>narrateur|Léa rejoint un mot. Maman sourit. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8379,6 +8425,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8546,6 +8593,7 @@
           <t>narrateur|Léa a choisi la boîte. Un oiseau chante. maman montre lentement. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8737,6 +8785,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8904,6 +8953,7 @@
           <t>narrateur|Léa rejoint un câlin. Le sol est frais. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9071,6 +9121,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9238,6 +9289,7 @@
           <t>narrateur|Léa rejoint une aide. Maman sourit. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9405,6 +9457,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9572,6 +9625,7 @@
           <t>narrateur|Léa rejoint un mot. Le lait est blanc. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9739,6 +9793,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9906,6 +9961,7 @@
           <t>narrateur|Léa a choisi le torchon. Le sol est frais. maman montre lentement. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10097,6 +10153,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10264,6 +10321,7 @@
           <t>narrateur|Léa rejoint un câlin. Maman sourit. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10431,6 +10489,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10598,6 +10657,7 @@
           <t>narrateur|Léa rejoint une aide. Le lait est blanc. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10765,6 +10825,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10932,6 +10993,7 @@
           <t>narrateur|Léa rejoint un mot. Une cuillère tinte. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. l'évier, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11099,6 +11161,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11266,6 +11329,7 @@
           <t>narrateur|Léa va vers le placard. Le bois est lisse. maman est tout près. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11449,6 +11513,7 @@
           <t>narrateur|C'est trop difficile. Que fait Léa ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11620,6 +11685,7 @@
           <t>narrateur|C'est juste. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. Léa donne la main à maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11811,6 +11877,7 @@
           <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11978,6 +12045,7 @@
           <t>narrateur|Léa a choisi le bocal. Maman sourit. maman montre lentement. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12169,6 +12237,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12336,6 +12405,7 @@
           <t>narrateur|Léa rejoint un câlin. Le sol est frais. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12503,6 +12573,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12670,6 +12741,7 @@
           <t>narrateur|Léa rejoint une aide. Maman sourit. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12837,6 +12909,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13004,6 +13077,7 @@
           <t>narrateur|Léa rejoint un mot. Le lait est blanc. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le bocal.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13171,6 +13245,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13338,6 +13413,7 @@
           <t>narrateur|Léa a choisi la boîte. Le lait est blanc. maman montre lentement. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13529,6 +13605,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13696,6 +13773,7 @@
           <t>narrateur|Léa rejoint un câlin. Maman sourit. Léa va dire le besoin. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13863,6 +13941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14030,6 +14109,7 @@
           <t>narrateur|Léa rejoint une aide. Le lait est blanc. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14197,6 +14277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14364,6 +14445,7 @@
           <t>narrateur|Léa rejoint un mot. Une cuillère tinte. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis la boîte.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14531,6 +14613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14698,6 +14781,7 @@
           <t>narrateur|Léa a choisi le torchon. Une cuillère tinte. maman montre lentement. Léa appelle maman. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14889,6 +14973,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15056,6 +15141,7 @@
           <t>narrateur|Léa rejoint un câlin. Le lait est blanc. Léa va vers eux. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15223,6 +15309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15390,6 +15477,7 @@
           <t>narrateur|Léa rejoint une aide. Une cuillère tinte. Léa attend l'aide. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15557,6 +15645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15724,6 +15813,7 @@
           <t>narrateur|Léa rejoint un mot. Ça sent le pain. Léa dit merci. Léa va aller vers eux. Elle va dire le besoin. Elle appelle maman. maman dit merci. le placard, puis le torchon.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15891,6 +15981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15909,7 +16000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15933,6 +16024,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15947,7 +16052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16134,6 +16239,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
